--- a/py_solution/result3.xlsx
+++ b/py_solution/result3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题5" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="问题5结果" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,22 +424,22 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>航向角rad</t>
+          <t>航向角(rad)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>航向角°</t>
+          <t>航向角(°)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>速度m/s</t>
+          <t>飞行速度(m/s)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>弹编号</t>
+          <t>烟幕弹编号</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -449,47 +449,47 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>投放时间s</t>
+          <t>投放时间(s)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>延时s</t>
+          <t>起爆延时(s)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>投放X</t>
+          <t>投放点X</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>投放Y</t>
+          <t>投放点Y</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>投放Z</t>
+          <t>投放点Z</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>起爆X</t>
+          <t>起爆点X</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>起爆Y</t>
+          <t>起爆点Y</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>起爆Z</t>
+          <t>起爆点Z</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>总时长s</t>
+          <t>总有效遮蔽时长(s)</t>
         </is>
       </c>
     </row>
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.135131</v>
+        <v>3.131636</v>
       </c>
       <c r="C2" t="n">
-        <v>179.6297</v>
+        <v>179.4295</v>
       </c>
       <c r="D2" t="n">
-        <v>120</v>
+        <v>119.97</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -517,31 +517,31 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.7944</v>
+        <v>0.3535</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4014</v>
+        <v>3.663</v>
       </c>
       <c r="I2" t="n">
-        <v>17704.67</v>
+        <v>17757.6</v>
       </c>
       <c r="J2" t="n">
-        <v>0.62</v>
+        <v>0.42</v>
       </c>
       <c r="K2" t="n">
         <v>1800</v>
       </c>
       <c r="L2" t="n">
-        <v>17296.51</v>
+        <v>17318.16</v>
       </c>
       <c r="M2" t="n">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="N2" t="n">
-        <v>1743.31</v>
+        <v>1734.25</v>
       </c>
       <c r="O2" t="n">
-        <v>5.835</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="3">
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.135131</v>
+        <v>3.131636</v>
       </c>
       <c r="C3" t="n">
-        <v>179.6297</v>
+        <v>179.4295</v>
       </c>
       <c r="D3" t="n">
-        <v>120</v>
+        <v>119.97</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -568,28 +568,28 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1.7944</v>
+        <v>1.3725</v>
       </c>
       <c r="H3" t="n">
-        <v>3.4262</v>
+        <v>2.0866</v>
       </c>
       <c r="I3" t="n">
-        <v>17584.67</v>
+        <v>17635.35</v>
       </c>
       <c r="J3" t="n">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="K3" t="n">
         <v>1800</v>
       </c>
       <c r="L3" t="n">
-        <v>17173.54</v>
+        <v>17385.02</v>
       </c>
       <c r="M3" t="n">
-        <v>4.05</v>
+        <v>4.13</v>
       </c>
       <c r="N3" t="n">
-        <v>1742.48</v>
+        <v>1778.67</v>
       </c>
     </row>
     <row r="4">
@@ -599,13 +599,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.135131</v>
+        <v>3.131636</v>
       </c>
       <c r="C4" t="n">
-        <v>179.6297</v>
+        <v>179.4295</v>
       </c>
       <c r="D4" t="n">
-        <v>120</v>
+        <v>119.97</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -616,28 +616,28 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2.7944</v>
+        <v>3.4762</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1536</v>
+        <v>4.8254</v>
       </c>
       <c r="I4" t="n">
-        <v>17464.67</v>
+        <v>17382.98</v>
       </c>
       <c r="J4" t="n">
-        <v>2.17</v>
+        <v>4.15</v>
       </c>
       <c r="K4" t="n">
         <v>1800</v>
       </c>
       <c r="L4" t="n">
-        <v>16966.26</v>
+        <v>16804.09</v>
       </c>
       <c r="M4" t="n">
-        <v>5.39</v>
+        <v>9.92</v>
       </c>
       <c r="N4" t="n">
-        <v>1715.46</v>
+        <v>1685.9</v>
       </c>
     </row>
     <row r="5">
@@ -647,13 +647,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.750642</v>
+        <v>-2.243326</v>
       </c>
       <c r="C5" t="n">
-        <v>-100.3044</v>
+        <v>-128.5331</v>
       </c>
       <c r="D5" t="n">
-        <v>120</v>
+        <v>119.84</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -664,28 +664,28 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5.0166</v>
+        <v>5.1629</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6291</v>
+        <v>5.5189</v>
       </c>
       <c r="I5" t="n">
-        <v>11892.32</v>
+        <v>11614.57</v>
       </c>
       <c r="J5" t="n">
-        <v>807.71</v>
+        <v>916.02</v>
       </c>
       <c r="K5" t="n">
         <v>1400</v>
       </c>
       <c r="L5" t="n">
-        <v>11814.42</v>
+        <v>11202.56</v>
       </c>
       <c r="M5" t="n">
-        <v>379.25</v>
+        <v>398.67</v>
       </c>
       <c r="N5" t="n">
-        <v>1335.47</v>
+        <v>1250.76</v>
       </c>
     </row>
     <row r="6">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.750642</v>
+        <v>-2.243326</v>
       </c>
       <c r="C6" t="n">
-        <v>-100.3044</v>
+        <v>-128.5331</v>
       </c>
       <c r="D6" t="n">
-        <v>120</v>
+        <v>119.84</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
@@ -712,47 +712,47 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>6.0166</v>
+        <v>6.6471</v>
       </c>
       <c r="H6" t="n">
-        <v>6.4477</v>
+        <v>7.7761</v>
       </c>
       <c r="I6" t="n">
-        <v>11870.85</v>
+        <v>11503.76</v>
       </c>
       <c r="J6" t="n">
-        <v>689.65</v>
+        <v>776.88</v>
       </c>
       <c r="K6" t="n">
         <v>1400</v>
       </c>
       <c r="L6" t="n">
-        <v>11732.45</v>
+        <v>10923.24</v>
       </c>
       <c r="M6" t="n">
-        <v>-71.59999999999999</v>
+        <v>47.93</v>
       </c>
       <c r="N6" t="n">
-        <v>1196.29</v>
+        <v>1103.71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FY5</t>
+          <t>FY2</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.218529</v>
+        <v>-2.243326</v>
       </c>
       <c r="C7" t="n">
-        <v>127.1124</v>
+        <v>-128.5331</v>
       </c>
       <c r="D7" t="n">
-        <v>120</v>
+        <v>119.84</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -760,76 +760,460 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>13.5973</v>
+        <v>8.120699999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5274</v>
+        <v>6.8894</v>
       </c>
       <c r="I7" t="n">
-        <v>12015.48</v>
+        <v>11393.76</v>
       </c>
       <c r="J7" t="n">
-        <v>-698.8099999999999</v>
+        <v>638.75</v>
       </c>
       <c r="K7" t="n">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="L7" t="n">
-        <v>11760.07</v>
+        <v>10879.43</v>
       </c>
       <c r="M7" t="n">
-        <v>-361.26</v>
+        <v>-7.08</v>
       </c>
       <c r="N7" t="n">
-        <v>1239.03</v>
+        <v>1167.43</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>FY3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.767001</v>
+      </c>
+      <c r="C8" t="n">
+        <v>158.5375</v>
+      </c>
+      <c r="D8" t="n">
+        <v>93.43000000000001</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1.4608</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5872.99</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-2950.06</v>
+      </c>
+      <c r="K8" t="n">
+        <v>700</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5729.52</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-2893.66</v>
+      </c>
+      <c r="N8" t="n">
+        <v>686.66</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FY3</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.767001</v>
+      </c>
+      <c r="C9" t="n">
+        <v>158.5375</v>
+      </c>
+      <c r="D9" t="n">
+        <v>93.43000000000001</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>2.8983</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5748</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-2900.92</v>
+      </c>
+      <c r="K9" t="n">
+        <v>700</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5604.53</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-2844.52</v>
+      </c>
+      <c r="N9" t="n">
+        <v>686.66</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FY3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.767001</v>
+      </c>
+      <c r="C10" t="n">
+        <v>158.5375</v>
+      </c>
+      <c r="D10" t="n">
+        <v>93.43000000000001</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>4.6475</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.0963</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5595.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-2841.13</v>
+      </c>
+      <c r="K10" t="n">
+        <v>700</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5326.68</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-2735.28</v>
+      </c>
+      <c r="N10" t="n">
+        <v>653.02</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FY4</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-2.906802</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-166.5475</v>
+      </c>
+      <c r="D11" t="n">
+        <v>110</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.1548</v>
+      </c>
+      <c r="I11" t="n">
+        <v>10960.79</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1990.62</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10730.26</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1935.48</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1777.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FY4</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-2.906802</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-166.5475</v>
+      </c>
+      <c r="D12" t="n">
+        <v>110</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>2.3664</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.1951</v>
+      </c>
+      <c r="I12" t="n">
+        <v>10746.83</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1939.44</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L12" t="n">
+        <v>10405.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1857.68</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1749.98</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FY4</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-2.906802</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-166.5475</v>
+      </c>
+      <c r="D13" t="n">
+        <v>110</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>3.4488</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.2409</v>
+      </c>
+      <c r="I13" t="n">
+        <v>10631.04</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1911.74</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L13" t="n">
+        <v>10177.33</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1803.22</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1711.87</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>FY5</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>2.218529</v>
-      </c>
-      <c r="C8" t="n">
-        <v>127.1124</v>
-      </c>
-      <c r="D8" t="n">
-        <v>120</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="B14" t="n">
+        <v>1.795125</v>
+      </c>
+      <c r="C14" t="n">
+        <v>102.8531</v>
+      </c>
+      <c r="D14" t="n">
+        <v>119.42</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>13.709</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.2558</v>
+      </c>
+      <c r="I14" t="n">
+        <v>12635.81</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-403.87</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L14" t="n">
+        <v>12522.76</v>
+      </c>
+      <c r="M14" t="n">
+        <v>91.62</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1211.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FY5</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.795125</v>
+      </c>
+      <c r="C15" t="n">
+        <v>102.8531</v>
+      </c>
+      <c r="D15" t="n">
+        <v>119.42</v>
+      </c>
+      <c r="E15" t="n">
         <v>2</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>15.6276</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5.0516</v>
-      </c>
-      <c r="I8" t="n">
-        <v>11868.48</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-504.53</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="G15" t="n">
+        <v>14.7096</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.5437</v>
+      </c>
+      <c r="I15" t="n">
+        <v>12609.23</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-287.38</v>
+      </c>
+      <c r="K15" t="n">
         <v>1300</v>
       </c>
-      <c r="L8" t="n">
-        <v>11502.71</v>
-      </c>
-      <c r="M8" t="n">
-        <v>-21.12</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1174.96</v>
+      <c r="L15" t="n">
+        <v>12541.66</v>
+      </c>
+      <c r="M15" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1268.3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FY5</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.795125</v>
+      </c>
+      <c r="C16" t="n">
+        <v>102.8531</v>
+      </c>
+      <c r="D16" t="n">
+        <v>119.42</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>15.9957</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.5494</v>
+      </c>
+      <c r="I16" t="n">
+        <v>12575.07</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-137.64</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L16" t="n">
+        <v>12533.91</v>
+      </c>
+      <c r="M16" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1288.24</v>
       </c>
     </row>
   </sheetData>
